--- a/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
@@ -498,7 +498,6 @@
           <t>01 5616110</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore componenti/equipaggiamento elettrico Ex (marchio Stahl); attivita' principale protezione antideflagrante, ingrosso materiale elettrico. Fondata 2013, sede Rapska 26/1, Zagabria.</t>
@@ -711,7 +710,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Installazione, riparazione, manutenzione e collaudo impianti/attrezzature elettriche antideflagranti (stazioni servizio, raffinerie, depositi carburanti). Opera anche col marchio storico Piraex. 113 dipendenti (2025).</t>
+          <t>Installazione, riparazione, manutenzione e collaudo impianti/attrezzature elettriche antideflagranti (stazioni servizio, raffinerie, depositi carburanti). Opera anche col marchio storico Piraex. 113 dipendenti (2025). [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -788,7 +787,6 @@
           <t>031 251155</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Ente/istituto sicurezza sul lavoro; sezione dedicata 'Protueksplozijska zastita (Ex)': classificazione aree a rischio, manuali Ex, test impianti elettrici in atmosfera esplosiva.</t>
@@ -826,7 +824,6 @@
           <t>+385 1 5578565</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Ente di certificazione IECEx e Notified Body EU n. 2829 per direttiva ATEX 2014/34/EU; servizio B2B a produttori/distributori. NOTA: indirizzo aggiornato risulta Karlovacka cesta 197, Zagabria-Lucko (diverso da quello nella fonte grezza) - verificare prima dell'uso commerciale.</t>
@@ -871,7 +868,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Filiale croata del produttore tedesco BERLINERLUFT TECHNIK GmbH; categoria prodotto dedicata 'Ex ventilatori' con modelli certificati ATEX.</t>
+          <t>Filiale croata del produttore tedesco BERLINERLUFT TECHNIK GmbH; categoria prodotto dedicata 'Ex ventilatori' con modelli certificati ATEX. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore/service autorizzato Nilfisk; confermata presenza in catalogo di modelli specifici ATEX.</t>
+          <t>Distributore/service autorizzato Nilfisk; confermata presenza in catalogo di modelli specifici ATEX. [DUPLICATO — vedi anche: 2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore componenti/equipaggiamento elettrico Ex (marchio Stahl); attivita' principale protezione antideflagrante, ingrosso materiale elettrico. Fondata 2013, sede Rapska 26/1, Zagabria.</t>
+          <t>Distributore componenti/equipaggiamento elettrico Ex (marchio Stahl); attivita' principale protezione antideflagrante, ingrosso materiale elettrico. Fondata 2013, sede Rapska 26/1, Zagabria. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service provider B2B: ispezioni periodiche e manutenzione impianti/attrezzature Ex secondo HRN EN 60079-17. Azienda del 1993.</t>
+          <t>Service provider B2B: ispezioni periodiche e manutenzione impianti/attrezzature Ex secondo HRN EN 60079-17. Azienda del 1993. [DUPLICATO — vedi anche: 2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Service provider specializzato in ispezione/manutenzione Ex (metodo SafeEx, RFID); unita' organizzativa dedicata ATEX sul sito.</t>
+          <t>Service provider specializzato in ispezione/manutenzione Ex (metodo SafeEx, RFID); unita' organizzativa dedicata ATEX sul sito. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Progettazione/produzione/installazione sistemi di aspirazione, filtrazione e trasporto pneumatico; sezione dedicata 'Ex izvedba' conforme a Direttiva ATEX 2014/34/EU. Dal 1994, 30 dipendenti.</t>
+          <t>Progettazione/produzione/installazione sistemi di aspirazione, filtrazione e trasporto pneumatico; sezione dedicata 'Ex izvedba' conforme a Direttiva ATEX 2014/34/EU. Dal 1994, 30 dipendenti. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Filiale croata di SMC (automazione pneumatica); pagina prodotto dedicata 'ATEX proizvodi' con valvole, cilindri, trasduttori certificati Ex.</t>
+          <t>Filiale croata di SMC (automazione pneumatica); pagina prodotto dedicata 'ATEX proizvodi' con valvole, cilindri, trasduttori certificati Ex. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ente/istituto sicurezza sul lavoro; sezione dedicata 'Protueksplozijska zastita (Ex)': classificazione aree a rischio, manuali Ex, test impianti elettrici in atmosfera esplosiva.</t>
+          <t>Ente/istituto sicurezza sul lavoro; sezione dedicata 'Protueksplozijska zastita (Ex)': classificazione aree a rischio, manuali Ex, test impianti elettrici in atmosfera esplosiva. [DUPLICATO — vedi anche: 2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ente di certificazione IECEx e Notified Body EU n. 2829 per direttiva ATEX 2014/34/EU; servizio B2B a produttori/distributori. NOTA: indirizzo aggiornato risulta Karlovacka cesta 197, Zagabria-Lucko (diverso da quello nella fonte grezza) - verificare prima dell'uso commerciale.</t>
+          <t>Ente di certificazione IECEx e Notified Body EU n. 2829 per direttiva ATEX 2014/34/EU; servizio B2B a produttori/distributori. NOTA: indirizzo aggiornato risulta Karlovacka cesta 197, Zagabria-Lucko (diverso da quello nella fonte grezza) - verificare prima dell'uso commerciale. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-21_06_Croazia_Dubrovačko-neretvanska_ATEX_Equipment-Services.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Distributore aspiratori industriali monofase/trifase/diesel/a batteria/pneumatici certificati per zone ATEX; anche sistemi di stoccaggio/trasporto pneumatico.</t>
+          <t>Distributore aspiratori industriali monofase/trifase/diesel/a batteria/pneumatici certificati per zone ATEX; anche sistemi di stoccaggio/trasporto pneumatico. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
